--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/maule.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4328.97</v>
+        <v>4310.32</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8476.84</v>
+        <v>8323.120000000001</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>17499.26</v>
+        <v>17593.49</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>55673.9</v>
+        <v>56088.66</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>43072.51</v>
+        <v>42966.15</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>23171.93</v>
+        <v>23285.75</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>64756.16</v>
+        <v>65203.25</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>8717.219999999999</v>
+        <v>8777.41</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8608.190000000001</v>
+        <v>8585.42</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>11069.49</v>
+        <v>10922.04</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>17256.2</v>
+        <v>17420.11</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4124.73</v>
+        <v>4166.03</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,68 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4833.67</v>
+        <v>4866.02</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1495207-11-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>11707.46</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/maule.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/maule.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Maule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Maule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1307,7 +1307,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1495207-11-CM26</t>
+          <t>4451-470-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES TOGUITA SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.549.439-5</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,7 +1362,312 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
+        <v>6031.07</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>675-43-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>61.402.019-9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>David Isaac</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>10942.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4451-503-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>69.110.500-8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>TRANSPORTES TOGUITA SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.549.439-5</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>6504.94</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1495207-11-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.981.340-5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
         <v>11707.46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2291-1412-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rentur Chile SpA </t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.241.697-2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>5705.32</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2291-1414-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MARPACIFICO SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>77.173.533-9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>6978.05</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/maule.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -676,7 +676,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTUR CHILE SPA </t>
+          <t xml:space="preserve">Rentur Chile SpA </t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTUR CHILE SPA </t>
+          <t xml:space="preserve">Rentur Chile SpA </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENTUR CHILE SPA </t>
+          <t xml:space="preserve">Rentur Chile SpA </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1668,6 +1668,311 @@
       </c>
       <c r="M20" s="2" t="n">
         <v>6978.05</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5056-3060-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.606.901-2</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ABRAHAM PATRICIO VILLANUEVA MICHEA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>15.751.336-2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>5334.84</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1469-2627-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BUSES VILLAR</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.465.610-5</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>56713.22</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1199-213-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BUSES VILLAR</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.465.610-5</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>38554.16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1469-2817-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>BUSES VILLAR</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>76.465.610-5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>35010.51</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1469-2823-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>933.51</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/maule.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/maule.xlsx
@@ -745,7 +745,11 @@
           <t>77.173.533-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +810,11 @@
           <t>77.173.533-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>77.549.439-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>77.171.057-3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>77.173.533-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1253,11 @@
           <t>77.173.533-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1318,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>77.549.439-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>77.549.439-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1574,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1700,11 @@
           <t>77.173.533-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1765,11 @@
           <t>15.751.336-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2013,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/maule.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2025,6 +2025,132 @@
       </c>
       <c r="M25" s="2" t="n">
         <v>933.51</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1469-3198-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BUSES VILLAR</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>76.465.610-5</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>2540.42</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2292-7344-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>11670.52</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/maule.xlsx
+++ b/docs/oc-regiones/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/maule.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
